--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-17.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-17.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583988087180</v>
+        <v>5595991592211</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jammerson</t>
+          <t>Wanderlene</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jammerson Gomes Soares</t>
+          <t>Wanderlene de Melo Costa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583987242179</v>
+        <v>5583986187703</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Djacir</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Julio Rafael da Silva Marinho</t>
+          <t>Djacir Pereira Meirelhes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583988274029</v>
+        <v>5583991657537</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wellygton</t>
+          <t>Gilberto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wellygton Mendonca dos Santos</t>
+          <t>Gilberto Barbosa de Lima Filho</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5584987227042</v>
+        <v>5583986070196</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Davi</t>
+          <t>Gilson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Davi de Carvalho Diniz Melo</t>
+          <t>Gilson Alexandre Silva</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583981963681</v>
+        <v>5583981479481</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Andrea da Costa Bohac de Haro</t>
+          <t>Manuel Silvio</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583996906861</v>
+        <v>5583999855056</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aercio</t>
+          <t>Djalma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aercio Sales de Almeida</t>
+          <t>Djalma Dias Ramalho</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583998156004</v>
+        <v>5583987105020</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Glacai</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Glacai</t>
+          <t>Fabio Jose Farias Aguiar</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583993455252</v>
+        <v>5583988564555</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Jeova</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paulo Roberto Soares de Castro</t>
+          <t>Jeova Luiz dos Santos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583993059171</v>
+        <v>5583999158598</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Waldenice</t>
+          <t>Ivanildo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Waldenice Batista</t>
+          <t>Ivanildo Ribeiro de Souza</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583986079008</v>
+        <v>5583999124334</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rubens</t>
+          <t>Walmir</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rubens Gomes da Silva</t>
+          <t>Walmir Braz</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583996905477</v>
+        <v>5583986712237</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roseane</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Roseane Silva de Oliveira</t>
+          <t>Ana Paula de Almeida Lima</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583998845164</v>
+        <v>5583988087180</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hellen</t>
+          <t>Jammerson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hellen Karolyne Marques de Santana</t>
+          <t>Jammerson Gomes Soares</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583987099867</v>
+        <v>5583987242179</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paulo Carneiro Gomes</t>
+          <t>Julio Rafael da Silva Marinho</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583986048385</v>
+        <v>5583988274029</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Josafa</t>
+          <t>Wellygton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Josafa Dionisio da Silva</t>
+          <t>Wellygton Mendonca dos Santos</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583987413264</v>
+        <v>5584987227042</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Edivaldo</t>
+          <t>Davi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edivaldo Trajano Bezerra</t>
+          <t>Davi de Carvalho Diniz Melo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583988130329</v>
+        <v>5583981963681</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Erick</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Erick Costa</t>
+          <t>Andrea da Costa Bohac de Haro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583988383395</v>
+        <v>5583996906861</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ednaldo</t>
+          <t>Aercio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ednaldo Soares de Souza</t>
+          <t>Aercio Sales de Almeida</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583987705584</v>
+        <v>5583998156004</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Elvis</t>
+          <t>Glacai</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Elvis Gutemberg da Silva Freitas</t>
+          <t>Glacai</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583986563234</v>
+        <v>5583998629977</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Rinaldo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maria Yasmim Silveira de Carvalho</t>
+          <t>Rinaldo Souza Magalhaes</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583981208930</v>
+        <v>5583993455252</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Savio</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Savio Luiz Dantas da Costa</t>
+          <t>Paulo Roberto Soares de Castro</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5581996958425</v>
+        <v>5583993059171</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Italo</t>
+          <t>Waldenice</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italo Augusto Leal</t>
+          <t>Waldenice Batista</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583991235781</v>
+        <v>5583986079008</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Rubens</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maxwell Florentino da Silva</t>
+          <t>Rubens Gomes da Silva</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583986821701</v>
+        <v>5583996905477</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Willams</t>
+          <t>Roseane</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Willams do Nascimento Brito</t>
+          <t>Roseane Silva de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5511952740988</v>
+        <v>5583998845164</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jerlaine</t>
+          <t>Hellen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jerlaine Santos de Figueiredo</t>
+          <t>Hellen Karolyne Marques de Santana</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5538991882190</v>
+        <v>5583987099867</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stéphanie</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stéphanie Oliveira Nina Rocha</t>
+          <t>Paulo Carneiro Gomes</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583987249013</v>
+        <v>5583986048385</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Josafa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felipe Raphael Queiroz Sobral</t>
+          <t>Josafa Dionisio da Silva</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583986054738</v>
+        <v>5583987413264</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Edivaldo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rafael Salustiano</t>
+          <t>Edivaldo Trajano Bezerra</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583996973880</v>
+        <v>5583988130329</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Erick</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nathan Dalmeida Alves de Oliveira</t>
+          <t>Erick Costa</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988030628</v>
+        <v>5583988383395</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Ednaldo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Andre Teixeira da Rocha</t>
+          <t>Ednaldo Soares de Souza</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583986157108</v>
+        <v>5583987705584</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Elvis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Joana Darc Pereira Diniz</t>
+          <t>Elvis Gutemberg da Silva Freitas</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583987735881</v>
+        <v>5583986563234</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Esdras</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Esdras Marques de Souza</t>
+          <t>Maria Yasmim Silveira de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583988388617</v>
+        <v>5583981208930</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Savio</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington Santos</t>
+          <t>Savio Luiz Dantas da Costa</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583991564599</v>
+        <v>5581996958425</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Italo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fabio Costa Silva</t>
+          <t>Italo Augusto Leal</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583991369563</v>
+        <v>5583991235781</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Geilson</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Geilson Cavalcanti de Oliveira</t>
+          <t>Maxwell Florentino da Silva</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583996558390</v>
+        <v>5583986821701</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jokitan</t>
+          <t>Willams</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jokitan dos Santos Moreira</t>
+          <t>Willams do Nascimento Brito</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5511954556831</v>
+        <v>5511952740988</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Demetrio</t>
+          <t>Jerlaine</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Demetrio Almeida</t>
+          <t>Jerlaine Santos de Figueiredo</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583996105930</v>
+        <v>5538991882190</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Stéphanie</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Maria da Penha Souza do Nascimento</t>
+          <t>Stéphanie Oliveira Nina Rocha</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583986569045</v>
+        <v>5583987249013</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Helio Nascimento Guedes</t>
+          <t>Felipe Raphael Queiroz Sobral</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5521967363838</v>
+        <v>5583986054738</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Francinaldo</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Francinaldo Fernandes dos Santos</t>
+          <t>Rafael Salustiano</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583993214959</v>
+        <v>5583996973880</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maria das Gracas Barbosa de Moura</t>
+          <t>Nathan Dalmeida Alves de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583987561090</v>
+        <v>5583988030628</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tania</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tania Maria da Silva</t>
+          <t>Andre Teixeira da Rocha</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583981674469</v>
+        <v>5583986157108</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tiago</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tiago Santos</t>
+          <t>Joana Darc Pereira Diniz</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5511973220000</v>
+        <v>5583987735881</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Esdras</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sergio Namur</t>
+          <t>Esdras Marques de Souza</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583991311521</v>
+        <v>5583988388617</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Humberto</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Humberto Cardoso</t>
+          <t>Washington Santos</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583996722636</v>
+        <v>5583991564599</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jose Humberth Pereira</t>
+          <t>Fabio Costa Silva</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583986401948</v>
+        <v>5583991369563</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Geilson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Camila de Medeiros Dantas</t>
+          <t>Geilson Cavalcanti de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583999393622</v>
+        <v>5583996558390</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Jokitan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Joao Batista de Sousa</t>
+          <t>Jokitan dos Santos Moreira</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583991662277</v>
+        <v>5511954556831</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Demetrio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lucas Marciel de Castro Silva</t>
+          <t>Demetrio Almeida</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583991577535</v>
+        <v>5583996105930</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Carlos Antonio da Silva</t>
+          <t>Maria da Penha Souza do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583988891862</v>
+        <v>5583986569045</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Christian Oliveira de Lucena</t>
+          <t>Helio Nascimento Guedes</t>
         </is>
       </c>
     </row>
